--- a/Excel/Avg/Rata-rata-16.xlsx
+++ b/Excel/Avg/Rata-rata-16.xlsx
@@ -620,22 +620,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>0.0007407000000000001</v>
+        <v>0.0008548999999999999</v>
       </c>
       <c r="C2">
-        <v>0.0004917999999999999</v>
+        <v>0.0005911</v>
       </c>
       <c r="D2">
-        <v>0.0003865</v>
+        <v>0.0010209</v>
       </c>
       <c r="E2">
-        <v>0.0005914</v>
+        <v>0.0011984</v>
       </c>
       <c r="F2">
-        <v>0.0007778</v>
+        <v>0.0016603</v>
       </c>
       <c r="G2">
-        <v>0.0005976400000000001</v>
+        <v>0.00106512</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -643,22 +643,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.0004103</v>
+        <v>0.0004642</v>
       </c>
       <c r="C3">
-        <v>0.0003133</v>
+        <v>0.0003427</v>
       </c>
       <c r="D3">
-        <v>0.0002352</v>
+        <v>0.0002705</v>
       </c>
       <c r="E3">
-        <v>0.0002717</v>
+        <v>0.0003027</v>
       </c>
       <c r="F3">
-        <v>0.0002619</v>
+        <v>0.0003118</v>
       </c>
       <c r="G3">
-        <v>0.00029848</v>
+        <v>0.00033838</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -666,22 +666,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>0.0008</v>
+        <v>0.0009182999999999998</v>
       </c>
       <c r="C4">
-        <v>0.0004566</v>
+        <v>0.0005102999999999999</v>
       </c>
       <c r="D4">
-        <v>0.0004279</v>
+        <v>0.0005079</v>
       </c>
       <c r="E4">
-        <v>0.0004195</v>
+        <v>0.0004679</v>
       </c>
       <c r="F4">
-        <v>0.0003812000000000001</v>
+        <v>0.0004746</v>
       </c>
       <c r="G4">
-        <v>0.00049704</v>
+        <v>0.0005757999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -689,22 +689,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.0007454</v>
+        <v>0.0008697999999999999</v>
       </c>
       <c r="C5">
-        <v>0.0004279</v>
+        <v>0.0004811</v>
       </c>
       <c r="D5">
-        <v>0.0003262</v>
+        <v>0.0004005</v>
       </c>
       <c r="E5">
-        <v>0.0004524</v>
+        <v>0.000516</v>
       </c>
       <c r="F5">
-        <v>0.0006205000000000001</v>
+        <v>0.0007223000000000002</v>
       </c>
       <c r="G5">
-        <v>0.00051448</v>
+        <v>0.0005979400000000001</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -712,22 +712,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.0005559</v>
+        <v>0.0006215000000000001</v>
       </c>
       <c r="C6">
-        <v>0.0003675</v>
+        <v>0.0004469</v>
       </c>
       <c r="D6">
-        <v>0.0004274</v>
+        <v>0.0004985</v>
       </c>
       <c r="E6">
-        <v>0.0004586</v>
+        <v>0.0005169</v>
       </c>
       <c r="F6">
-        <v>0.000642</v>
+        <v>0.0007488999999999999</v>
       </c>
       <c r="G6">
-        <v>0.0004902800000000001</v>
+        <v>0.00056654</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -735,22 +735,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0.0007801</v>
+        <v>0.0008932</v>
       </c>
       <c r="C7">
-        <v>0.0005912</v>
+        <v>0.0006338</v>
       </c>
       <c r="D7">
-        <v>0.0004503</v>
+        <v>0.0009121999999999999</v>
       </c>
       <c r="E7">
-        <v>0.0006463</v>
+        <v>0.0007202000000000001</v>
       </c>
       <c r="F7">
-        <v>0.0008284000000000002</v>
+        <v>0.0012178</v>
       </c>
       <c r="G7">
-        <v>0.0006592600000000001</v>
+        <v>0.0008754399999999999</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -758,22 +758,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>0.0008073000000000001</v>
+        <v>0.0009738</v>
       </c>
       <c r="C8">
-        <v>0.0005350000000000001</v>
+        <v>0.0006249000000000001</v>
       </c>
       <c r="D8">
-        <v>0.0004223</v>
+        <v>0.0009191</v>
       </c>
       <c r="E8">
-        <v>0.0005737</v>
+        <v>0.0007356</v>
       </c>
       <c r="F8">
-        <v>0.0010001</v>
+        <v>0.0013468</v>
       </c>
       <c r="G8">
-        <v>0.00066768</v>
+        <v>0.0009200400000000001</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -781,22 +781,22 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>0.0004872</v>
+        <v>0.0005817</v>
       </c>
       <c r="C9">
-        <v>0.0004888</v>
+        <v>0.0005881</v>
       </c>
       <c r="D9">
-        <v>0.0003112999999999999</v>
+        <v>0.0003905</v>
       </c>
       <c r="E9">
-        <v>0.0004062</v>
+        <v>0.0004237000000000001</v>
       </c>
       <c r="F9">
-        <v>0.000401</v>
+        <v>0.000629</v>
       </c>
       <c r="G9">
-        <v>0.0004189</v>
+        <v>0.0005226</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -804,22 +804,22 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>0.0003429</v>
+        <v>0.0003887</v>
       </c>
       <c r="C10">
-        <v>0.0003373</v>
+        <v>0.0003936</v>
       </c>
       <c r="D10">
-        <v>0.0002051</v>
+        <v>0.0002355</v>
       </c>
       <c r="E10">
-        <v>0.0003114</v>
+        <v>0.0003563</v>
       </c>
       <c r="F10">
-        <v>0.0003341</v>
+        <v>0.0004785999999999999</v>
       </c>
       <c r="G10">
-        <v>0.0003061599999999999</v>
+        <v>0.00037054</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -827,22 +827,22 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>0.000427</v>
+        <v>0.0005514</v>
       </c>
       <c r="C11">
-        <v>0.0003606</v>
+        <v>0.0003916</v>
       </c>
       <c r="D11">
-        <v>0.0002812</v>
+        <v>0.0003224</v>
       </c>
       <c r="E11">
-        <v>0.0003051</v>
+        <v>0.0003416000000000001</v>
       </c>
       <c r="F11">
-        <v>0.0003074</v>
+        <v>0.0003505</v>
       </c>
       <c r="G11">
-        <v>0.00033626</v>
+        <v>0.0003915</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -850,22 +850,22 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>0.0004355</v>
+        <v>0.0004908</v>
       </c>
       <c r="C12">
-        <v>0.0003624</v>
+        <v>0.0003967</v>
       </c>
       <c r="D12">
-        <v>0.0002506</v>
+        <v>0.0003055</v>
       </c>
       <c r="E12">
-        <v>0.0003507</v>
+        <v>0.0004079</v>
       </c>
       <c r="F12">
-        <v>0.0003516999999999999</v>
+        <v>0.0004717</v>
       </c>
       <c r="G12">
-        <v>0.00035018</v>
+        <v>0.00041452</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -873,22 +873,22 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>0.0008449</v>
+        <v>0.0010179</v>
       </c>
       <c r="C13">
-        <v>0.0004934999999999999</v>
+        <v>0.0005535</v>
       </c>
       <c r="D13">
-        <v>0.0005059</v>
+        <v>0.0005555</v>
       </c>
       <c r="E13">
-        <v>0.0004394000000000001</v>
+        <v>0.0004976000000000001</v>
       </c>
       <c r="F13">
-        <v>0.0004306</v>
+        <v>0.0005074</v>
       </c>
       <c r="G13">
-        <v>0.00054286</v>
+        <v>0.0006263799999999999</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -896,22 +896,22 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>0.0009634999999999999</v>
+        <v>0.0011176</v>
       </c>
       <c r="C14">
-        <v>0.0005176</v>
+        <v>0.0005721</v>
       </c>
       <c r="D14">
-        <v>0.0004391</v>
+        <v>0.0005078</v>
       </c>
       <c r="E14">
-        <v>0.0004438</v>
+        <v>0.0004994</v>
       </c>
       <c r="F14">
-        <v>0.0004580999999999999</v>
+        <v>0.0005422999999999999</v>
       </c>
       <c r="G14">
-        <v>0.0005644199999999999</v>
+        <v>0.00064784</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -919,22 +919,22 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>0.0009227</v>
+        <v>0.0010662</v>
       </c>
       <c r="C15">
-        <v>0.0005542</v>
+        <v>0.0006104999999999999</v>
       </c>
       <c r="D15">
-        <v>0.000515</v>
+        <v>0.0005962999999999999</v>
       </c>
       <c r="E15">
-        <v>0.0004275</v>
+        <v>0.0004717</v>
       </c>
       <c r="F15">
-        <v>0.0006663000000000001</v>
+        <v>0.0007276</v>
       </c>
       <c r="G15">
-        <v>0.0006171400000000001</v>
+        <v>0.0006944599999999999</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -942,22 +942,22 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>0.0007974</v>
+        <v>0.0009322</v>
       </c>
       <c r="C16">
-        <v>0.0004581</v>
+        <v>0.0005687000000000001</v>
       </c>
       <c r="D16">
-        <v>0.0003872</v>
+        <v>0.0004374</v>
       </c>
       <c r="E16">
-        <v>0.0004996</v>
+        <v>0.0005529</v>
       </c>
       <c r="F16">
-        <v>0.0006510999999999999</v>
+        <v>0.0007559999999999999</v>
       </c>
       <c r="G16">
-        <v>0.00055868</v>
+        <v>0.0006494399999999999</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -965,22 +965,22 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>0.0007744</v>
+        <v>0.0009434000000000002</v>
       </c>
       <c r="C17">
-        <v>0.0005802000000000001</v>
+        <v>0.0006602</v>
       </c>
       <c r="D17">
-        <v>0.0003732</v>
+        <v>0.0004442</v>
       </c>
       <c r="E17">
-        <v>0.0004639</v>
+        <v>0.0006082</v>
       </c>
       <c r="F17">
-        <v>0.0005857</v>
+        <v>0.0007365</v>
       </c>
       <c r="G17">
-        <v>0.00055548</v>
+        <v>0.0006785000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -988,22 +988,22 @@
         <v>23</v>
       </c>
       <c r="B18">
-        <v>0.0004264000000000001</v>
+        <v>0.0005078</v>
       </c>
       <c r="C18">
-        <v>0.0003708</v>
+        <v>0.0004237999999999999</v>
       </c>
       <c r="D18">
-        <v>0.0002903</v>
+        <v>0.0003388</v>
       </c>
       <c r="E18">
-        <v>0.0003618</v>
+        <v>0.0004138</v>
       </c>
       <c r="F18">
-        <v>0.0004311</v>
+        <v>0.000479</v>
       </c>
       <c r="G18">
-        <v>0.00037608</v>
+        <v>0.0004326399999999999</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1011,22 +1011,22 @@
         <v>24</v>
       </c>
       <c r="B19">
-        <v>0.0004348999999999999</v>
+        <v>0.0005537000000000001</v>
       </c>
       <c r="C19">
-        <v>0.0003208</v>
+        <v>0.0003689</v>
       </c>
       <c r="D19">
-        <v>0.0003562</v>
+        <v>0.0004166</v>
       </c>
       <c r="E19">
-        <v>0.0003118</v>
+        <v>0.0003539</v>
       </c>
       <c r="F19">
-        <v>0.0003523</v>
+        <v>0.0004092</v>
       </c>
       <c r="G19">
-        <v>0.0003552</v>
+        <v>0.00042046</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1034,22 +1034,22 @@
         <v>25</v>
       </c>
       <c r="B20">
-        <v>0.0005702999999999999</v>
+        <v>0.0006623</v>
       </c>
       <c r="C20">
-        <v>0.0003701</v>
+        <v>0.0004236</v>
       </c>
       <c r="D20">
-        <v>0.0003747</v>
+        <v>0.0004431999999999999</v>
       </c>
       <c r="E20">
-        <v>0.0004029</v>
+        <v>0.0004407</v>
       </c>
       <c r="F20">
-        <v>0.0005379</v>
+        <v>0.0006198</v>
       </c>
       <c r="G20">
-        <v>0.00045118</v>
+        <v>0.0005179200000000001</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1057,22 +1057,22 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>0.0005624</v>
+        <v>0.0006709999999999999</v>
       </c>
       <c r="C21">
-        <v>0.0004107000000000001</v>
+        <v>0.0004696</v>
       </c>
       <c r="D21">
-        <v>0.0004781</v>
+        <v>0.0005326</v>
       </c>
       <c r="E21">
-        <v>0.0004939</v>
+        <v>0.0006171999999999999</v>
       </c>
       <c r="F21">
-        <v>0.0006656</v>
+        <v>0.0008007</v>
       </c>
       <c r="G21">
-        <v>0.00052214</v>
+        <v>0.0006182199999999999</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1080,22 +1080,22 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>0.0005455</v>
+        <v>0.0006921</v>
       </c>
       <c r="C22">
-        <v>0.0003565</v>
+        <v>0.0004110000000000001</v>
       </c>
       <c r="D22">
-        <v>0.0004663000000000001</v>
+        <v>0.0005658</v>
       </c>
       <c r="E22">
-        <v>0.0004522</v>
+        <v>0.0005453999999999999</v>
       </c>
       <c r="F22">
-        <v>0.0006387000000000001</v>
+        <v>0.0007492</v>
       </c>
       <c r="G22">
-        <v>0.0004918400000000001</v>
+        <v>0.0005927</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1103,22 +1103,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>0.0008457999999999999</v>
+        <v>0.0009846</v>
       </c>
       <c r="C23">
-        <v>0.0005857</v>
+        <v>0.0006953999999999999</v>
       </c>
       <c r="D23">
-        <v>0.0004693</v>
+        <v>0.0008081</v>
       </c>
       <c r="E23">
-        <v>0.0006191000000000001</v>
+        <v>0.0008147</v>
       </c>
       <c r="F23">
-        <v>0.0010258</v>
+        <v>0.0011974</v>
       </c>
       <c r="G23">
-        <v>0.0007091399999999999</v>
+        <v>0.0009000399999999998</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1126,22 +1126,22 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>0.0005317000000000001</v>
+        <v>0.0006171999999999999</v>
       </c>
       <c r="C24">
-        <v>0.0005301</v>
+        <v>0.0005889000000000001</v>
       </c>
       <c r="D24">
-        <v>0.000357</v>
+        <v>0.0004455</v>
       </c>
       <c r="E24">
-        <v>0.0004171</v>
+        <v>0.0005018000000000001</v>
       </c>
       <c r="F24">
-        <v>0.0004445</v>
+        <v>0.0005022</v>
       </c>
       <c r="G24">
-        <v>0.00045608</v>
+        <v>0.0005311199999999999</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1149,22 +1149,22 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>0.0005423</v>
+        <v>0.0006690999999999999</v>
       </c>
       <c r="C25">
-        <v>0.0005136</v>
+        <v>0.0005595</v>
       </c>
       <c r="D25">
-        <v>0.0003804</v>
+        <v>0.0004371</v>
       </c>
       <c r="E25">
-        <v>0.0004269</v>
+        <v>0.0004745</v>
       </c>
       <c r="F25">
-        <v>0.0004292</v>
+        <v>0.0005104999999999999</v>
       </c>
       <c r="G25">
-        <v>0.00045848</v>
+        <v>0.0005301399999999999</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1172,22 +1172,22 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>0.0005289</v>
+        <v>0.0006137</v>
       </c>
       <c r="C26">
-        <v>0.0005476000000000001</v>
+        <v>0.0006172</v>
       </c>
       <c r="D26">
-        <v>0.0003497</v>
+        <v>0.0003936</v>
       </c>
       <c r="E26">
-        <v>0.0004447</v>
+        <v>0.0005118</v>
       </c>
       <c r="F26">
-        <v>0.000687</v>
+        <v>0.000897</v>
       </c>
       <c r="G26">
-        <v>0.0005115800000000001</v>
+        <v>0.00060666</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1195,22 +1195,22 @@
         <v>32</v>
       </c>
       <c r="B27">
-        <v>0.0003904</v>
+        <v>0.0004340999999999999</v>
       </c>
       <c r="C27">
-        <v>0.0004094</v>
+        <v>0.0004429</v>
       </c>
       <c r="D27">
-        <v>0.0002511</v>
+        <v>0.0002793</v>
       </c>
       <c r="E27">
-        <v>0.0003541</v>
+        <v>0.0003953</v>
       </c>
       <c r="F27">
-        <v>0.0003971000000000001</v>
+        <v>0.0004843</v>
       </c>
       <c r="G27">
-        <v>0.00036042</v>
+        <v>0.0004071799999999999</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1218,22 +1218,22 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>0.0003991</v>
+        <v>0.0004687</v>
       </c>
       <c r="C28">
-        <v>0.0003836</v>
+        <v>0.0004322</v>
       </c>
       <c r="D28">
-        <v>0.0002686</v>
+        <v>0.0002739</v>
       </c>
       <c r="E28">
-        <v>0.0003646</v>
+        <v>0.0004237000000000001</v>
       </c>
       <c r="F28">
-        <v>0.0003496</v>
+        <v>0.0004449</v>
       </c>
       <c r="G28">
-        <v>0.0003531</v>
+        <v>0.0004086800000000001</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1241,22 +1241,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>0.0004798</v>
+        <v>0.0005466000000000001</v>
       </c>
       <c r="C29">
-        <v>0.000419</v>
+        <v>0.0004383</v>
       </c>
       <c r="D29">
-        <v>0.0003063</v>
+        <v>0.0003487</v>
       </c>
       <c r="E29">
-        <v>0.0003893000000000001</v>
+        <v>0.000441</v>
       </c>
       <c r="F29">
-        <v>0.000404</v>
+        <v>0.0006961000000000001</v>
       </c>
       <c r="G29">
-        <v>0.00039968</v>
+        <v>0.00049414</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1264,22 +1264,22 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>0.0009962000000000003</v>
+        <v>0.0011653</v>
       </c>
       <c r="C30">
-        <v>0.0005853</v>
+        <v>0.0006329</v>
       </c>
       <c r="D30">
-        <v>0.0004891</v>
+        <v>0.0005559</v>
       </c>
       <c r="E30">
-        <v>0.0005120999999999999</v>
+        <v>0.0005558000000000001</v>
       </c>
       <c r="F30">
-        <v>0.0004976000000000001</v>
+        <v>0.0005766</v>
       </c>
       <c r="G30">
-        <v>0.0006160600000000001</v>
+        <v>0.0006973</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1287,22 +1287,22 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>0.0009992999999999998</v>
+        <v>0.0011218</v>
       </c>
       <c r="C31">
-        <v>0.0005932999999999999</v>
+        <v>0.0006383</v>
       </c>
       <c r="D31">
-        <v>0.0005433</v>
+        <v>0.0006232000000000001</v>
       </c>
       <c r="E31">
-        <v>0.0004598</v>
+        <v>0.0005245</v>
       </c>
       <c r="F31">
-        <v>0.0006967</v>
+        <v>0.0007712999999999999</v>
       </c>
       <c r="G31">
-        <v>0.0006584799999999998</v>
+        <v>0.0007358200000000001</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1310,22 +1310,22 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>0.0009961999999999998</v>
+        <v>0.0012125</v>
       </c>
       <c r="C32">
-        <v>0.0006016000000000001</v>
+        <v>0.0006629</v>
       </c>
       <c r="D32">
-        <v>0.0004685000000000001</v>
+        <v>0.0006074</v>
       </c>
       <c r="E32">
-        <v>0.0004541</v>
+        <v>0.0005288000000000001</v>
       </c>
       <c r="F32">
-        <v>0.0007064999999999999</v>
+        <v>0.0008271999999999999</v>
       </c>
       <c r="G32">
-        <v>0.0006453799999999999</v>
+        <v>0.0007677600000000001</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1333,22 +1333,22 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>0.0008156</v>
+        <v>0.0009611</v>
       </c>
       <c r="C33">
-        <v>0.0006204</v>
+        <v>0.0007229000000000001</v>
       </c>
       <c r="D33">
-        <v>0.0004171</v>
+        <v>0.0004892</v>
       </c>
       <c r="E33">
-        <v>0.0005053999999999999</v>
+        <v>0.0006238999999999999</v>
       </c>
       <c r="F33">
-        <v>0.0006578999999999999</v>
+        <v>0.0008042</v>
       </c>
       <c r="G33">
-        <v>0.00060328</v>
+        <v>0.0007202600000000001</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1356,22 +1356,22 @@
         <v>39</v>
       </c>
       <c r="B34">
-        <v>0.0004229</v>
+        <v>0.0005008000000000001</v>
       </c>
       <c r="C34">
-        <v>0.0004412</v>
+        <v>0.0004999</v>
       </c>
       <c r="D34">
-        <v>0.0003085</v>
+        <v>0.0003758</v>
       </c>
       <c r="E34">
-        <v>0.0003438</v>
+        <v>0.0003953</v>
       </c>
       <c r="F34">
-        <v>0.0004718</v>
+        <v>0.0005621000000000001</v>
       </c>
       <c r="G34">
-        <v>0.00039764</v>
+        <v>0.00046678</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1379,22 +1379,22 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>0.0002601</v>
+        <v>0.0003163</v>
       </c>
       <c r="C35">
-        <v>0.0003275</v>
+        <v>0.0003424</v>
       </c>
       <c r="D35">
-        <v>0.0002498</v>
+        <v>0.0002926</v>
       </c>
       <c r="E35">
-        <v>0.0003766</v>
+        <v>0.0004274999999999999</v>
       </c>
       <c r="F35">
-        <v>0.0004967</v>
+        <v>0.0005581</v>
       </c>
       <c r="G35">
-        <v>0.00034214</v>
+        <v>0.00038738</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1402,22 +1402,22 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>0.0004631</v>
+        <v>0.0005467999999999998</v>
       </c>
       <c r="C36">
-        <v>0.0004182</v>
+        <v>0.0004632000000000001</v>
       </c>
       <c r="D36">
-        <v>0.0003365</v>
+        <v>0.0003872</v>
       </c>
       <c r="E36">
-        <v>0.0003968999999999999</v>
+        <v>0.0004522</v>
       </c>
       <c r="F36">
-        <v>0.0004633</v>
+        <v>0.0005207</v>
       </c>
       <c r="G36">
-        <v>0.0004156</v>
+        <v>0.00047402</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1425,22 +1425,22 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>0.0003868</v>
+        <v>0.0005599</v>
       </c>
       <c r="C37">
-        <v>0.0004134</v>
+        <v>0.0004388</v>
       </c>
       <c r="D37">
-        <v>0.0003236</v>
+        <v>0.0003786999999999999</v>
       </c>
       <c r="E37">
-        <v>0.0003399</v>
+        <v>0.0004152</v>
       </c>
       <c r="F37">
-        <v>0.0003911</v>
+        <v>0.0004917</v>
       </c>
       <c r="G37">
-        <v>0.00037096</v>
+        <v>0.0004568599999999999</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1448,22 +1448,22 @@
         <v>43</v>
       </c>
       <c r="B38">
-        <v>0.0004904999999999999</v>
+        <v>0.0005762999999999999</v>
       </c>
       <c r="C38">
-        <v>0.0003688</v>
+        <v>0.0004321</v>
       </c>
       <c r="D38">
-        <v>0.0003852</v>
+        <v>0.000452</v>
       </c>
       <c r="E38">
-        <v>0.0003416</v>
+        <v>0.000388</v>
       </c>
       <c r="F38">
-        <v>0.0003952999999999999</v>
+        <v>0.0004456</v>
       </c>
       <c r="G38">
-        <v>0.00039628</v>
+        <v>0.0004587999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1471,22 +1471,22 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>0.0004544</v>
+        <v>0.0005331000000000001</v>
       </c>
       <c r="C39">
-        <v>0.0003561</v>
+        <v>0.0003845</v>
       </c>
       <c r="D39">
-        <v>0.000343</v>
+        <v>0.0004087</v>
       </c>
       <c r="E39">
-        <v>0.0003249</v>
+        <v>0.0003635</v>
       </c>
       <c r="F39">
-        <v>0.0003601</v>
+        <v>0.0004234</v>
       </c>
       <c r="G39">
-        <v>0.0003677</v>
+        <v>0.0004226400000000001</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1494,22 +1494,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>0.0005122</v>
+        <v>0.0005972000000000001</v>
       </c>
       <c r="C40">
-        <v>0.0003326</v>
+        <v>0.0004204</v>
       </c>
       <c r="D40">
-        <v>0.0003698</v>
+        <v>0.0004275999999999999</v>
       </c>
       <c r="E40">
-        <v>0.0002982</v>
+        <v>0.0003525000000000001</v>
       </c>
       <c r="F40">
-        <v>0.0003950000000000001</v>
+        <v>0.0004482</v>
       </c>
       <c r="G40">
-        <v>0.00038156</v>
+        <v>0.00044918</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1517,22 +1517,22 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>0.0006249999999999999</v>
+        <v>0.0006966</v>
       </c>
       <c r="C41">
-        <v>0.0004115</v>
+        <v>0.0004677</v>
       </c>
       <c r="D41">
-        <v>0.0004327</v>
+        <v>0.0004825</v>
       </c>
       <c r="E41">
-        <v>0.0004123</v>
+        <v>0.0004725999999999999</v>
       </c>
       <c r="F41">
-        <v>0.0005711000000000001</v>
+        <v>0.0006531</v>
       </c>
       <c r="G41">
-        <v>0.00049052</v>
+        <v>0.0005545</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1540,22 +1540,22 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>0.0006505</v>
+        <v>0.0006975</v>
       </c>
       <c r="C42">
-        <v>0.0003965</v>
+        <v>0.0004416000000000001</v>
       </c>
       <c r="D42">
-        <v>0.0003994</v>
+        <v>0.0004753</v>
       </c>
       <c r="E42">
-        <v>0.0003877</v>
+        <v>0.0004411</v>
       </c>
       <c r="F42">
-        <v>0.0005524</v>
+        <v>0.0006322</v>
       </c>
       <c r="G42">
-        <v>0.0004772999999999999</v>
+        <v>0.00053754</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1563,22 +1563,22 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>0.0005898</v>
+        <v>0.0007245</v>
       </c>
       <c r="C43">
-        <v>0.0003989999999999999</v>
+        <v>0.0004464</v>
       </c>
       <c r="D43">
-        <v>0.0005004</v>
+        <v>0.0005754999999999999</v>
       </c>
       <c r="E43">
-        <v>0.0005020000000000001</v>
+        <v>0.0005634</v>
       </c>
       <c r="F43">
-        <v>0.000694</v>
+        <v>0.0008028999999999999</v>
       </c>
       <c r="G43">
-        <v>0.0005370400000000001</v>
+        <v>0.00062254</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1586,22 +1586,22 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>0.0006048000000000001</v>
+        <v>0.0006962</v>
       </c>
       <c r="C44">
-        <v>0.0005765999999999999</v>
+        <v>0.0005911999999999998</v>
       </c>
       <c r="D44">
-        <v>0.0004187</v>
+        <v>0.0004735</v>
       </c>
       <c r="E44">
-        <v>0.0004674</v>
+        <v>0.0005276</v>
       </c>
       <c r="F44">
-        <v>0.0005165</v>
+        <v>0.0006701999999999999</v>
       </c>
       <c r="G44">
-        <v>0.0005168</v>
+        <v>0.00059174</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1609,22 +1609,22 @@
         <v>50</v>
       </c>
       <c r="B45">
-        <v>0.0005555</v>
+        <v>0.0006515</v>
       </c>
       <c r="C45">
-        <v>0.0006001</v>
+        <v>0.0006777999999999999</v>
       </c>
       <c r="D45">
-        <v>0.0004037</v>
+        <v>0.0004548</v>
       </c>
       <c r="E45">
-        <v>0.0004758</v>
+        <v>0.0005525</v>
       </c>
       <c r="F45">
-        <v>0.0007601</v>
+        <v>0.0008867</v>
       </c>
       <c r="G45">
-        <v>0.00055904</v>
+        <v>0.00064466</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1632,22 +1632,22 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>0.0005543</v>
+        <v>0.0006615000000000001</v>
       </c>
       <c r="C46">
-        <v>0.0006345</v>
+        <v>0.0006900000000000001</v>
       </c>
       <c r="D46">
-        <v>0.000398</v>
+        <v>0.0004104</v>
       </c>
       <c r="E46">
-        <v>0.0004544999999999999</v>
+        <v>0.0005304</v>
       </c>
       <c r="F46">
-        <v>0.0007051999999999999</v>
+        <v>0.000845</v>
       </c>
       <c r="G46">
-        <v>0.0005493</v>
+        <v>0.00062746</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1655,22 +1655,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>0.0004518</v>
+        <v>0.0005196000000000001</v>
       </c>
       <c r="C47">
-        <v>0.0004358</v>
+        <v>0.0004955999999999999</v>
       </c>
       <c r="D47">
-        <v>0.0003128</v>
+        <v>0.0003216000000000001</v>
       </c>
       <c r="E47">
-        <v>0.0004086</v>
+        <v>0.0004828000000000001</v>
       </c>
       <c r="F47">
-        <v>0.0004032999999999999</v>
+        <v>0.0004893999999999999</v>
       </c>
       <c r="G47">
-        <v>0.00040246</v>
+        <v>0.0004617999999999999</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1678,22 +1678,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>0.0010834</v>
+        <v>0.0013039</v>
       </c>
       <c r="C48">
-        <v>0.0006459</v>
+        <v>0.0006928</v>
       </c>
       <c r="D48">
-        <v>0.0005257</v>
+        <v>0.0006418</v>
       </c>
       <c r="E48">
-        <v>0.0004901</v>
+        <v>0.0005488</v>
       </c>
       <c r="F48">
-        <v>0.0007434000000000001</v>
+        <v>0.0008946000000000001</v>
       </c>
       <c r="G48">
-        <v>0.0006977000000000001</v>
+        <v>0.00081638</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1701,22 +1701,22 @@
         <v>54</v>
       </c>
       <c r="B49">
-        <v>0.0004573</v>
+        <v>0.0005386</v>
       </c>
       <c r="C49">
-        <v>0.0005031</v>
+        <v>0.0005466000000000002</v>
       </c>
       <c r="D49">
-        <v>0.0003535</v>
+        <v>0.0004063</v>
       </c>
       <c r="E49">
-        <v>0.0003855</v>
+        <v>0.0004462</v>
       </c>
       <c r="F49">
-        <v>0.0005126</v>
+        <v>0.0005802000000000001</v>
       </c>
       <c r="G49">
-        <v>0.0004424</v>
+        <v>0.00050358</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1724,22 +1724,22 @@
         <v>55</v>
       </c>
       <c r="B50">
-        <v>0.0004141</v>
+        <v>0.0005975000000000002</v>
       </c>
       <c r="C50">
-        <v>0.0004328</v>
+        <v>0.0004872</v>
       </c>
       <c r="D50">
-        <v>0.0003485</v>
+        <v>0.0003498</v>
       </c>
       <c r="E50">
-        <v>0.0004071</v>
+        <v>0.0004161000000000001</v>
       </c>
       <c r="F50">
-        <v>0.0004163999999999999</v>
+        <v>0.0005584</v>
       </c>
       <c r="G50">
-        <v>0.00040378</v>
+        <v>0.0004818</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1747,22 +1747,22 @@
         <v>56</v>
       </c>
       <c r="B51">
-        <v>0.0003168</v>
+        <v>0.0003821</v>
       </c>
       <c r="C51">
-        <v>0.0003755</v>
+        <v>0.000438</v>
       </c>
       <c r="D51">
-        <v>0.0003246</v>
+        <v>0.0003844</v>
       </c>
       <c r="E51">
-        <v>0.0004605000000000001</v>
+        <v>0.0004867</v>
       </c>
       <c r="F51">
-        <v>0.0004467</v>
+        <v>0.0005249</v>
       </c>
       <c r="G51">
-        <v>0.00038482</v>
+        <v>0.0004432200000000001</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1770,22 +1770,22 @@
         <v>57</v>
       </c>
       <c r="B52">
-        <v>0.0003</v>
+        <v>0.0003457</v>
       </c>
       <c r="C52">
-        <v>0.000339</v>
+        <v>0.0003894</v>
       </c>
       <c r="D52">
-        <v>0.0002936</v>
+        <v>0.0003477</v>
       </c>
       <c r="E52">
-        <v>0.0004148</v>
+        <v>0.0004717</v>
       </c>
       <c r="F52">
-        <v>0.0005104</v>
+        <v>0.0005828</v>
       </c>
       <c r="G52">
-        <v>0.00037156</v>
+        <v>0.00042746</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1793,22 +1793,22 @@
         <v>58</v>
       </c>
       <c r="B53">
-        <v>0.0002973</v>
+        <v>0.0003338</v>
       </c>
       <c r="C53">
-        <v>0.0003228</v>
+        <v>0.0003724000000000001</v>
       </c>
       <c r="D53">
-        <v>0.0003143</v>
+        <v>0.0003034</v>
       </c>
       <c r="E53">
-        <v>0.0003947</v>
+        <v>0.0004251</v>
       </c>
       <c r="F53">
-        <v>0.0004326</v>
+        <v>0.0005710999999999999</v>
       </c>
       <c r="G53">
-        <v>0.00035234</v>
+        <v>0.0004011600000000001</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1816,22 +1816,22 @@
         <v>59</v>
       </c>
       <c r="B54">
-        <v>0.0004243</v>
+        <v>0.0005840999999999999</v>
       </c>
       <c r="C54">
-        <v>0.0004310000000000001</v>
+        <v>0.0005124</v>
       </c>
       <c r="D54">
-        <v>0.0003728000000000001</v>
+        <v>0.0004238999999999999</v>
       </c>
       <c r="E54">
-        <v>0.000393</v>
+        <v>0.0004497</v>
       </c>
       <c r="F54">
-        <v>0.0003967999999999999</v>
+        <v>0.0005405</v>
       </c>
       <c r="G54">
-        <v>0.0004035800000000001</v>
+        <v>0.00050212</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1839,22 +1839,22 @@
         <v>60</v>
       </c>
       <c r="B55">
-        <v>0.0005036</v>
+        <v>0.0005836</v>
       </c>
       <c r="C55">
-        <v>0.0003773</v>
+        <v>0.0004405</v>
       </c>
       <c r="D55">
-        <v>0.0003995</v>
+        <v>0.0005047000000000001</v>
       </c>
       <c r="E55">
-        <v>0.0003595</v>
+        <v>0.0003994</v>
       </c>
       <c r="F55">
-        <v>0.0004108000000000001</v>
+        <v>0.0004535</v>
       </c>
       <c r="G55">
-        <v>0.0004101400000000001</v>
+        <v>0.00047634</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1862,22 +1862,22 @@
         <v>61</v>
       </c>
       <c r="B56">
-        <v>0.0005664</v>
+        <v>0.000694</v>
       </c>
       <c r="C56">
-        <v>0.0003898</v>
+        <v>0.0004591</v>
       </c>
       <c r="D56">
-        <v>0.0003953999999999999</v>
+        <v>0.0004499</v>
       </c>
       <c r="E56">
-        <v>0.0003463</v>
+        <v>0.0003869</v>
       </c>
       <c r="F56">
-        <v>0.0004284</v>
+        <v>0.0004961999999999999</v>
       </c>
       <c r="G56">
-        <v>0.0004252600000000001</v>
+        <v>0.00049722</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1885,22 +1885,22 @@
         <v>62</v>
       </c>
       <c r="B57">
-        <v>0.0005223999999999999</v>
+        <v>0.0006123</v>
       </c>
       <c r="C57">
-        <v>0.0004279999999999999</v>
+        <v>0.0004070000000000001</v>
       </c>
       <c r="D57">
-        <v>0.000361</v>
+        <v>0.0004478999999999999</v>
       </c>
       <c r="E57">
-        <v>0.0003092</v>
+        <v>0.0003537</v>
       </c>
       <c r="F57">
-        <v>0.0003999</v>
+        <v>0.0004716</v>
       </c>
       <c r="G57">
-        <v>0.0004041</v>
+        <v>0.0004585</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1908,22 +1908,22 @@
         <v>63</v>
       </c>
       <c r="B58">
-        <v>0.0006255999999999999</v>
+        <v>0.0007440999999999999</v>
       </c>
       <c r="C58">
-        <v>0.0004308</v>
+        <v>0.0004814</v>
       </c>
       <c r="D58">
-        <v>0.0004349000000000001</v>
+        <v>0.0005195</v>
       </c>
       <c r="E58">
-        <v>0.0004246</v>
+        <v>0.0005074999999999999</v>
       </c>
       <c r="F58">
-        <v>0.0005735999999999998</v>
+        <v>0.0006634</v>
       </c>
       <c r="G58">
-        <v>0.0004979</v>
+        <v>0.00058318</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1931,22 +1931,22 @@
         <v>64</v>
       </c>
       <c r="B59">
-        <v>0.0006153</v>
+        <v>0.0007004</v>
       </c>
       <c r="C59">
-        <v>0.0007218000000000001</v>
+        <v>0.0007308000000000001</v>
       </c>
       <c r="D59">
-        <v>0.0004196</v>
+        <v>0.0004699</v>
       </c>
       <c r="E59">
-        <v>0.0005392</v>
+        <v>0.0005608</v>
       </c>
       <c r="F59">
-        <v>0.0007586</v>
+        <v>0.0010371</v>
       </c>
       <c r="G59">
-        <v>0.0006108999999999999</v>
+        <v>0.0006998000000000001</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1954,22 +1954,22 @@
         <v>65</v>
       </c>
       <c r="B60">
-        <v>0.0004642</v>
+        <v>0.0005924999999999999</v>
       </c>
       <c r="C60">
-        <v>0.0004704</v>
+        <v>0.0005377</v>
       </c>
       <c r="D60">
-        <v>0.0003943999999999999</v>
+        <v>0.0003942</v>
       </c>
       <c r="E60">
-        <v>0.0004412</v>
+        <v>0.0004704999999999999</v>
       </c>
       <c r="F60">
-        <v>0.0004424</v>
+        <v>0.0006234999999999999</v>
       </c>
       <c r="G60">
-        <v>0.00044252</v>
+        <v>0.00052368</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1977,22 +1977,22 @@
         <v>66</v>
       </c>
       <c r="B61">
-        <v>0.0003617</v>
+        <v>0.0004200000000000001</v>
       </c>
       <c r="C61">
-        <v>0.0004303999999999999</v>
+        <v>0.0004781000000000001</v>
       </c>
       <c r="D61">
-        <v>0.0003826</v>
+        <v>0.0004228</v>
       </c>
       <c r="E61">
-        <v>0.0004574</v>
+        <v>0.0005432000000000001</v>
       </c>
       <c r="F61">
-        <v>0.0004982</v>
+        <v>0.0005459</v>
       </c>
       <c r="G61">
-        <v>0.00042606</v>
+        <v>0.0004820000000000001</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2000,22 +2000,22 @@
         <v>67</v>
       </c>
       <c r="B62">
-        <v>0.0003448</v>
+        <v>0.0003857</v>
       </c>
       <c r="C62">
-        <v>0.0004373</v>
+        <v>0.0004775</v>
       </c>
       <c r="D62">
-        <v>0.0003373</v>
+        <v>0.0004055</v>
       </c>
       <c r="E62">
-        <v>0.0004398</v>
+        <v>0.0004974999999999999</v>
       </c>
       <c r="F62">
-        <v>0.0003871</v>
+        <v>0.0004331</v>
       </c>
       <c r="G62">
-        <v>0.00038926</v>
+        <v>0.00043986</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2023,22 +2023,22 @@
         <v>68</v>
       </c>
       <c r="B63">
-        <v>0.0003387999999999999</v>
+        <v>0.0003767</v>
       </c>
       <c r="C63">
-        <v>0.0003759</v>
+        <v>0.0004084</v>
       </c>
       <c r="D63">
-        <v>0.0003557</v>
+        <v>0.0003523</v>
       </c>
       <c r="E63">
-        <v>0.0004350000000000001</v>
+        <v>0.0004622</v>
       </c>
       <c r="F63">
-        <v>0.0004715</v>
+        <v>0.0006016000000000001</v>
       </c>
       <c r="G63">
-        <v>0.00039538</v>
+        <v>0.0004402400000000001</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2046,22 +2046,22 @@
         <v>69</v>
       </c>
       <c r="B64">
-        <v>0.0005491</v>
+        <v>0.0006628000000000001</v>
       </c>
       <c r="C64">
-        <v>0.0004195999999999999</v>
+        <v>0.0004451999999999999</v>
       </c>
       <c r="D64">
-        <v>0.0004158</v>
+        <v>0.0004955</v>
       </c>
       <c r="E64">
-        <v>0.0003492</v>
+        <v>0.0004257999999999999</v>
       </c>
       <c r="F64">
-        <v>0.0004404</v>
+        <v>0.0005011</v>
       </c>
       <c r="G64">
-        <v>0.00043482</v>
+        <v>0.00050608</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -2069,22 +2069,22 @@
         <v>70</v>
       </c>
       <c r="B65">
-        <v>0.0003677</v>
+        <v>0.0004511</v>
       </c>
       <c r="C65">
-        <v>0.0005395</v>
+        <v>0.0005128999999999999</v>
       </c>
       <c r="D65">
-        <v>0.0003821</v>
+        <v>0.0004559</v>
       </c>
       <c r="E65">
-        <v>0.0005185000000000001</v>
+        <v>0.0005396999999999999</v>
       </c>
       <c r="F65">
-        <v>0.0004175</v>
+        <v>0.0004892</v>
       </c>
       <c r="G65">
-        <v>0.0004450600000000001</v>
+        <v>0.0004897599999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2930,22 +2930,22 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C37">
         <v>17</v>
       </c>
       <c r="D37">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E37">
         <v>18</v>
       </c>
       <c r="F37">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G37">
-        <v>16</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -3304,16 +3304,16 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E53">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F53">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G53">
-        <v>16</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3321,7 +3321,7 @@
         <v>59</v>
       </c>
       <c r="B54">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C54">
         <v>11</v>
@@ -3333,10 +3333,10 @@
         <v>9</v>
       </c>
       <c r="F54">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G54">
-        <v>10.8</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -3436,7 +3436,7 @@
         <v>64</v>
       </c>
       <c r="B59">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C59">
         <v>12</v>
@@ -3451,7 +3451,7 @@
         <v>8</v>
       </c>
       <c r="G59">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3459,22 +3459,22 @@
         <v>65</v>
       </c>
       <c r="B60">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C60">
         <v>11</v>
       </c>
       <c r="D60">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E60">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F60">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G60">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3514,13 +3514,13 @@
         <v>19</v>
       </c>
       <c r="E62">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F62">
         <v>12</v>
       </c>
       <c r="G62">
-        <v>16.8</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3537,10 +3537,10 @@
         <v>16</v>
       </c>
       <c r="E63">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F63">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G63">
         <v>11.2</v>
@@ -3577,7 +3577,7 @@
         <v>12</v>
       </c>
       <c r="C65">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D65">
         <v>16</v>
@@ -3589,7 +3589,7 @@
         <v>7</v>
       </c>
       <c r="G65">
-        <v>11</v>
+        <v>11.2</v>
       </c>
     </row>
   </sheetData>
@@ -4320,7 +4320,7 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>27.55634918610405</v>
+        <v>29.21320343559643</v>
       </c>
       <c r="C32">
         <v>25.55634918610405</v>
@@ -4335,7 +4335,7 @@
         <v>24.97056274847714</v>
       </c>
       <c r="G32">
-        <v>25.67350647362943</v>
+        <v>26.0048773235279</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -4435,7 +4435,7 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>27.55634918610405</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="C37">
         <v>25.55634918610405</v>
@@ -4447,10 +4447,10 @@
         <v>23.55634918610405</v>
       </c>
       <c r="F37">
-        <v>25.31370849898476</v>
+        <v>22.97056274847714</v>
       </c>
       <c r="G37">
-        <v>25.45929291125633</v>
+        <v>24.54213562373095</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -4642,7 +4642,7 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>27.55634918610405</v>
+        <v>28.38477631085023</v>
       </c>
       <c r="C46">
         <v>27.55634918610405</v>
@@ -4657,7 +4657,7 @@
         <v>24.97056274847714</v>
       </c>
       <c r="G46">
-        <v>26.23919189857867</v>
+        <v>26.40487732352791</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -4688,7 +4688,7 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>27.55634918610405</v>
+        <v>28.92209549884099</v>
       </c>
       <c r="C48">
         <v>24.65008380450606</v>
@@ -4703,7 +4703,7 @@
         <v>24.24988430144958</v>
       </c>
       <c r="G48">
-        <v>25.18820701043266</v>
+        <v>25.46135627298005</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -4734,7 +4734,7 @@
         <v>55</v>
       </c>
       <c r="B50">
-        <v>27.55634918610405</v>
+        <v>31.55634918610405</v>
       </c>
       <c r="C50">
         <v>25.55634918610405</v>
@@ -4746,10 +4746,10 @@
         <v>23.55634918610405</v>
       </c>
       <c r="F50">
-        <v>23.55634918610405</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="G50">
-        <v>25.10782104868019</v>
+        <v>26.25929291125633</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -4812,13 +4812,13 @@
         <v>26.72792206135786</v>
       </c>
       <c r="E53">
-        <v>24.38477631085024</v>
+        <v>23.55634918610405</v>
       </c>
       <c r="F53">
-        <v>22.97056274847714</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="G53">
-        <v>25.67350647362943</v>
+        <v>25.74213562373096</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -4826,7 +4826,7 @@
         <v>59</v>
       </c>
       <c r="B54">
-        <v>27.55634918610405</v>
+        <v>25.06177259678004</v>
       </c>
       <c r="C54">
         <v>25.06177259678004</v>
@@ -4838,10 +4838,10 @@
         <v>23.08709566447531</v>
       </c>
       <c r="F54">
-        <v>24.99851445020445</v>
+        <v>22.52730043086546</v>
       </c>
       <c r="G54">
-        <v>25.20348807930973</v>
+        <v>24.21032995757712</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -4941,7 +4941,7 @@
         <v>64</v>
       </c>
       <c r="B59">
-        <v>27.33347333682185</v>
+        <v>28.16190046156803</v>
       </c>
       <c r="C59">
         <v>26.414373490278</v>
@@ -4956,7 +4956,7 @@
         <v>23.80662198383789</v>
       </c>
       <c r="G59">
-        <v>25.40152742743322</v>
+        <v>25.56721285238246</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -4973,13 +4973,13 @@
         <v>25.31370849898476</v>
       </c>
       <c r="E60">
-        <v>23.08709566447531</v>
+        <v>23.20005801635744</v>
       </c>
       <c r="F60">
-        <v>22.63292806537241</v>
+        <v>24.26221910942175</v>
       </c>
       <c r="G60">
-        <v>24.73037080234332</v>
+        <v>25.07882148152961</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -5013,19 +5013,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="C62">
-        <v>25.55634918610405</v>
+        <v>27.55634918610405</v>
       </c>
       <c r="D62">
         <v>26.72792206135786</v>
       </c>
       <c r="E62">
-        <v>26.38477631085023</v>
+        <v>23.55634918610405</v>
       </c>
       <c r="F62">
         <v>25.31370849898476</v>
       </c>
       <c r="G62">
-        <v>26.30782104868019</v>
+        <v>26.14213562373096</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -5042,13 +5042,13 @@
         <v>26.54977647648456</v>
       </c>
       <c r="E63">
-        <v>24.02848514110363</v>
+        <v>23.08709566447531</v>
       </c>
       <c r="F63">
-        <v>22.52730043086546</v>
+        <v>22.9781948590917</v>
       </c>
       <c r="G63">
-        <v>25.34342222434365</v>
+        <v>25.24532321466324</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -5082,7 +5082,7 @@
         <v>27.55634918610405</v>
       </c>
       <c r="C65">
-        <v>25.06177259678004</v>
+        <v>26.88362701190674</v>
       </c>
       <c r="D65">
         <v>26.54977647648456</v>
@@ -5094,7 +5094,7 @@
         <v>23.9102632953472</v>
       </c>
       <c r="G65">
-        <v>25.23305144383824</v>
+        <v>25.59742232686357</v>
       </c>
     </row>
   </sheetData>
@@ -5276,19 +5276,19 @@
         <v>22</v>
       </c>
       <c r="C8">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E8">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F8">
         <v>69</v>
       </c>
       <c r="G8">
-        <v>34.2</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -5365,13 +5365,13 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C12">
         <v>31</v>
       </c>
       <c r="D12">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E12">
         <v>40</v>
@@ -5380,7 +5380,7 @@
         <v>61</v>
       </c>
       <c r="G12">
-        <v>36.4</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -5411,10 +5411,10 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D14">
         <v>18</v>
@@ -5480,22 +5480,22 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C17">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D17">
         <v>18</v>
       </c>
       <c r="E17">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F17">
         <v>70</v>
       </c>
       <c r="G17">
-        <v>37.8</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -5621,19 +5621,19 @@
         <v>22</v>
       </c>
       <c r="C23">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D23">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E23">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F23">
         <v>69</v>
       </c>
       <c r="G23">
-        <v>34.2</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -5667,10 +5667,10 @@
         <v>33</v>
       </c>
       <c r="C25">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D25">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E25">
         <v>39</v>
@@ -5679,7 +5679,7 @@
         <v>45</v>
       </c>
       <c r="G25">
-        <v>35.4</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -5736,19 +5736,19 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D28">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E28">
         <v>42</v>
       </c>
       <c r="F28">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G28">
-        <v>36.6</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -5756,13 +5756,13 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C29">
         <v>31</v>
       </c>
       <c r="D29">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E29">
         <v>40</v>
@@ -5771,7 +5771,7 @@
         <v>61</v>
       </c>
       <c r="G29">
-        <v>36.4</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -5779,10 +5779,10 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D30">
         <v>18</v>
@@ -5825,13 +5825,13 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C32">
         <v>30</v>
       </c>
       <c r="D32">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E32">
         <v>37</v>
@@ -5840,7 +5840,7 @@
         <v>46</v>
       </c>
       <c r="G32">
-        <v>33.6</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -5848,22 +5848,22 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C33">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D33">
         <v>18</v>
       </c>
       <c r="E33">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F33">
         <v>70</v>
       </c>
       <c r="G33">
-        <v>37.8</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -5946,16 +5946,16 @@
         <v>15</v>
       </c>
       <c r="D37">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E37">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F37">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G37">
-        <v>12.8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -6104,10 +6104,10 @@
         <v>33</v>
       </c>
       <c r="C44">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D44">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E44">
         <v>39</v>
@@ -6116,7 +6116,7 @@
         <v>45</v>
       </c>
       <c r="G44">
-        <v>35.4</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -6147,10 +6147,10 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C46">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D46">
         <v>22</v>
@@ -6159,10 +6159,10 @@
         <v>40</v>
       </c>
       <c r="F46">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G46">
-        <v>36.8</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -6173,19 +6173,19 @@
         <v>33</v>
       </c>
       <c r="C47">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D47">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E47">
         <v>42</v>
       </c>
       <c r="F47">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G47">
-        <v>36.6</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -6193,13 +6193,13 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C48">
         <v>30</v>
       </c>
       <c r="D48">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E48">
         <v>37</v>
@@ -6208,7 +6208,7 @@
         <v>46</v>
       </c>
       <c r="G48">
-        <v>33.6</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -6239,22 +6239,22 @@
         <v>55</v>
       </c>
       <c r="B50">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C50">
         <v>13</v>
       </c>
       <c r="D50">
+        <v>10</v>
+      </c>
+      <c r="E50">
+        <v>15</v>
+      </c>
+      <c r="F50">
         <v>13</v>
       </c>
-      <c r="E50">
-        <v>18</v>
-      </c>
-      <c r="F50">
-        <v>10</v>
-      </c>
       <c r="G50">
-        <v>13.4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -6314,16 +6314,16 @@
         <v>13</v>
       </c>
       <c r="D53">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E53">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F53">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G53">
-        <v>14</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -6337,16 +6337,16 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E54">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F54">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G54">
-        <v>12.8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -6400,7 +6400,7 @@
         <v>62</v>
       </c>
       <c r="B57">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C57">
         <v>12</v>
@@ -6415,7 +6415,7 @@
         <v>7</v>
       </c>
       <c r="G57">
-        <v>10</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -6446,10 +6446,10 @@
         <v>64</v>
       </c>
       <c r="B59">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C59">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D59">
         <v>22</v>
@@ -6458,10 +6458,10 @@
         <v>40</v>
       </c>
       <c r="F59">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G59">
-        <v>36.8</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -6469,22 +6469,22 @@
         <v>65</v>
       </c>
       <c r="B60">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C60">
         <v>13</v>
       </c>
       <c r="D60">
+        <v>10</v>
+      </c>
+      <c r="E60">
+        <v>15</v>
+      </c>
+      <c r="F60">
         <v>13</v>
       </c>
-      <c r="E60">
-        <v>18</v>
-      </c>
-      <c r="F60">
-        <v>10</v>
-      </c>
       <c r="G60">
-        <v>13.4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -6518,13 +6518,13 @@
         <v>11</v>
       </c>
       <c r="C62">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D62">
         <v>12</v>
       </c>
       <c r="E62">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F62">
         <v>12</v>
@@ -6544,16 +6544,16 @@
         <v>13</v>
       </c>
       <c r="D63">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E63">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F63">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G63">
-        <v>14</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -6561,7 +6561,7 @@
         <v>69</v>
       </c>
       <c r="B64">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C64">
         <v>12</v>
@@ -6576,7 +6576,7 @@
         <v>7</v>
       </c>
       <c r="G64">
-        <v>10</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -6587,13 +6587,13 @@
         <v>11</v>
       </c>
       <c r="C65">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D65">
         <v>12</v>
       </c>
       <c r="E65">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F65">
         <v>12</v>
@@ -6787,13 +6787,13 @@
         <v>62</v>
       </c>
       <c r="E8">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F8">
         <v>89</v>
       </c>
       <c r="G8">
-        <v>76.40000000000001</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -6870,10 +6870,10 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C12">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D12">
         <v>46</v>
@@ -6885,7 +6885,7 @@
         <v>51</v>
       </c>
       <c r="G12">
-        <v>55.8</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -6916,10 +6916,10 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D14">
         <v>35</v>
@@ -6931,7 +6931,7 @@
         <v>21</v>
       </c>
       <c r="G14">
-        <v>34.4</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -6985,7 +6985,7 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C17">
         <v>64</v>
@@ -6994,13 +6994,13 @@
         <v>49</v>
       </c>
       <c r="E17">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F17">
         <v>51</v>
       </c>
       <c r="G17">
-        <v>57.8</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -7132,13 +7132,13 @@
         <v>62</v>
       </c>
       <c r="E23">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F23">
         <v>89</v>
       </c>
       <c r="G23">
-        <v>76.40000000000001</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -7169,13 +7169,13 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C25">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D25">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E25">
         <v>27</v>
@@ -7184,7 +7184,7 @@
         <v>28</v>
       </c>
       <c r="G25">
-        <v>35.4</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -7241,19 +7241,19 @@
         <v>55</v>
       </c>
       <c r="C28">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D28">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E28">
         <v>50</v>
       </c>
       <c r="F28">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G28">
-        <v>50</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -7261,10 +7261,10 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C29">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D29">
         <v>46</v>
@@ -7276,7 +7276,7 @@
         <v>51</v>
       </c>
       <c r="G29">
-        <v>55.8</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -7284,10 +7284,10 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C30">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D30">
         <v>35</v>
@@ -7299,7 +7299,7 @@
         <v>21</v>
       </c>
       <c r="G30">
-        <v>34.4</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -7330,10 +7330,10 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C32">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D32">
         <v>38</v>
@@ -7345,7 +7345,7 @@
         <v>28</v>
       </c>
       <c r="G32">
-        <v>37</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -7353,7 +7353,7 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C33">
         <v>64</v>
@@ -7362,13 +7362,13 @@
         <v>49</v>
       </c>
       <c r="E33">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F33">
         <v>51</v>
       </c>
       <c r="G33">
-        <v>57.8</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -7445,19 +7445,19 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C37">
         <v>30</v>
       </c>
       <c r="D37">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E37">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F37">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G37">
         <v>26</v>
@@ -7606,13 +7606,13 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C44">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D44">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E44">
         <v>27</v>
@@ -7621,7 +7621,7 @@
         <v>28</v>
       </c>
       <c r="G44">
-        <v>35.4</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -7655,7 +7655,7 @@
         <v>41</v>
       </c>
       <c r="C46">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D46">
         <v>33</v>
@@ -7667,7 +7667,7 @@
         <v>42</v>
       </c>
       <c r="G46">
-        <v>39.6</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -7678,19 +7678,19 @@
         <v>55</v>
       </c>
       <c r="C47">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D47">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E47">
         <v>50</v>
       </c>
       <c r="F47">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G47">
-        <v>50</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -7698,10 +7698,10 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C48">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D48">
         <v>38</v>
@@ -7713,7 +7713,7 @@
         <v>28</v>
       </c>
       <c r="G48">
-        <v>37</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -7744,22 +7744,22 @@
         <v>55</v>
       </c>
       <c r="B50">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C50">
         <v>27</v>
       </c>
       <c r="D50">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E50">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F50">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G50">
-        <v>23</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -7816,19 +7816,19 @@
         <v>17</v>
       </c>
       <c r="C53">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D53">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E53">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F53">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G53">
-        <v>22.8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -7836,19 +7836,19 @@
         <v>59</v>
       </c>
       <c r="B54">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C54">
         <v>30</v>
       </c>
       <c r="D54">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E54">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F54">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G54">
         <v>26</v>
@@ -7905,7 +7905,7 @@
         <v>62</v>
       </c>
       <c r="B57">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C57">
         <v>20</v>
@@ -7920,7 +7920,7 @@
         <v>15</v>
       </c>
       <c r="G57">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -7954,7 +7954,7 @@
         <v>41</v>
       </c>
       <c r="C59">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D59">
         <v>33</v>
@@ -7966,7 +7966,7 @@
         <v>42</v>
       </c>
       <c r="G59">
-        <v>39.6</v>
+        <v>39</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -7974,22 +7974,22 @@
         <v>65</v>
       </c>
       <c r="B60">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C60">
         <v>27</v>
       </c>
       <c r="D60">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E60">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F60">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G60">
-        <v>23</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -8023,19 +8023,19 @@
         <v>16</v>
       </c>
       <c r="C62">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D62">
         <v>22</v>
       </c>
       <c r="E62">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F62">
         <v>14</v>
       </c>
       <c r="G62">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -8046,19 +8046,19 @@
         <v>17</v>
       </c>
       <c r="C63">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D63">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E63">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F63">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G63">
-        <v>22.8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -8066,7 +8066,7 @@
         <v>69</v>
       </c>
       <c r="B64">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C64">
         <v>20</v>
@@ -8081,7 +8081,7 @@
         <v>15</v>
       </c>
       <c r="G64">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -8092,19 +8092,19 @@
         <v>16</v>
       </c>
       <c r="C65">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D65">
         <v>22</v>
       </c>
       <c r="E65">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F65">
         <v>14</v>
       </c>
       <c r="G65">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -8384,13 +8384,13 @@
         <v>13</v>
       </c>
       <c r="E12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F12">
         <v>5</v>
       </c>
       <c r="G12">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -8683,13 +8683,13 @@
         <v>14</v>
       </c>
       <c r="E25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F25">
         <v>6</v>
       </c>
       <c r="G25">
-        <v>10.2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -8950,7 +8950,7 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C37">
         <v>11</v>
@@ -8962,10 +8962,10 @@
         <v>10</v>
       </c>
       <c r="F37">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G37">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -9157,7 +9157,7 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C46">
         <v>12</v>
@@ -9172,7 +9172,7 @@
         <v>11</v>
       </c>
       <c r="G46">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -9249,22 +9249,22 @@
         <v>55</v>
       </c>
       <c r="B50">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C50">
         <v>11</v>
       </c>
       <c r="D50">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E50">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F50">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G50">
-        <v>10</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -9327,13 +9327,13 @@
         <v>15</v>
       </c>
       <c r="E53">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F53">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G53">
-        <v>10.4</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -9341,7 +9341,7 @@
         <v>59</v>
       </c>
       <c r="B54">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C54">
         <v>9</v>
@@ -9353,10 +9353,10 @@
         <v>7</v>
       </c>
       <c r="F54">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G54">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -9456,7 +9456,7 @@
         <v>64</v>
       </c>
       <c r="B59">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C59">
         <v>10</v>
@@ -9471,7 +9471,7 @@
         <v>6</v>
       </c>
       <c r="G59">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -9479,19 +9479,19 @@
         <v>65</v>
       </c>
       <c r="B60">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C60">
         <v>9</v>
       </c>
       <c r="D60">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E60">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G60">
         <v>8.6</v>
@@ -9528,19 +9528,19 @@
         <v>10</v>
       </c>
       <c r="C62">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D62">
         <v>15</v>
       </c>
       <c r="E62">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F62">
         <v>8</v>
       </c>
       <c r="G62">
-        <v>11</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -9557,10 +9557,10 @@
         <v>14</v>
       </c>
       <c r="E63">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F63">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G63">
         <v>9.199999999999999</v>
@@ -9597,7 +9597,7 @@
         <v>10</v>
       </c>
       <c r="C65">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D65">
         <v>14</v>
@@ -9609,7 +9609,7 @@
         <v>5</v>
       </c>
       <c r="G65">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>
